--- a/Arquivos/nao_atualizaveis/Ativo_IMES/Status - Base Controle e Lista de Espera - Ativo Imersão Executiva em Saúde Suplementar.xlsx
+++ b/Arquivos/nao_atualizaveis/Ativo_IMES/Status - Base Controle e Lista de Espera - Ativo Imersão Executiva em Saúde Suplementar.xlsx
@@ -5,33 +5,38 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ingrid.chaves\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\FIRJAN\Dashboard\dashboard-firjan\Arquivos\nao_atualizaveis\Ativo_IMES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72DFDADD-8620-454F-B53A-D853D3966F75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B54985C-CD11-41CE-AAF1-733B2D246348}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Resumo" sheetId="4" r:id="rId1"/>
-    <sheet name="Controle" sheetId="1" r:id="rId2"/>
-    <sheet name="LIsta de Espera" sheetId="2" r:id="rId3"/>
+    <sheet name="Confirmados" sheetId="5" r:id="rId2"/>
+    <sheet name="Controle" sheetId="1" r:id="rId3"/>
+    <sheet name="LIsta de Espera" sheetId="2" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Controle!$A$1:$O$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'LIsta de Espera'!$A$1:$Z$8</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
   <pivotCaches>
-    <pivotCache cacheId="13" r:id="rId4"/>
-    <pivotCache cacheId="17" r:id="rId5"/>
+    <pivotCache cacheId="20" r:id="rId5"/>
+    <pivotCache cacheId="24" r:id="rId6"/>
   </pivotCaches>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="kdIOys+aoabb4iBSSKZ16/431VjUxMclOOewTynTMQs="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId7" roundtripDataChecksum="kdIOys+aoabb4iBSSKZ16/431VjUxMclOOewTynTMQs="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="293">
   <si>
     <t>Title</t>
   </si>
@@ -796,9 +801,6 @@
     <t>Troca de Representante</t>
   </si>
   <si>
-    <t>Retornar ás 15:00 hrs</t>
-  </si>
-  <si>
     <t xml:space="preserve">Não tem mais interesse </t>
   </si>
   <si>
@@ -884,6 +886,36 @@
   </si>
   <si>
     <t>leandroquintanilha@transpetro.com.br</t>
+  </si>
+  <si>
+    <t>confirmado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troca de representante </t>
+  </si>
+  <si>
+    <t>Não tem interesse 02//10/26</t>
+  </si>
+  <si>
+    <t>Confirmou 02/10 ás 10:16</t>
+  </si>
+  <si>
+    <t>confirmou 02/10 ás 11:16</t>
+  </si>
+  <si>
+    <t>confirmou 02/10 ás 11:19</t>
+  </si>
+  <si>
+    <t>4° Tentativa 02/10 10:40</t>
+  </si>
+  <si>
+    <t>4° Tentativa 02/10 10:42</t>
+  </si>
+  <si>
+    <t>CONFIRMADOS LISTA OFICIAL</t>
+  </si>
+  <si>
+    <t>CONFIRMADOS LISTA DE ESPERA</t>
   </si>
 </sst>
 </file>
@@ -894,7 +926,7 @@
     <numFmt numFmtId="164" formatCode="d/m/yyyy\ hh:mm"/>
     <numFmt numFmtId="165" formatCode="d/m/yyyy"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -953,8 +985,26 @@
       <color rgb="FF467886"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -985,8 +1035,20 @@
         <bgColor rgb="FFFF0000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -1038,11 +1100,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF45B0E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1113,9 +1184,28 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="22" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="6" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="22" fontId="6" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1134,9 +1224,9 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Ingrid Geraldo Chaves" refreshedDate="46296.747117592589" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="45" xr:uid="{DB1C2AC3-16E0-4DA0-BF85-8352EA17132B}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Ingrid Geraldo Chaves" refreshedDate="46297.567641203706" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="46" xr:uid="{5F1A9A77-EA8D-416C-839A-8B57C91D55A5}">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A1:Z46" sheet="Controle"/>
+    <worksheetSource ref="A1:Z47" sheet="Controle"/>
   </cacheSource>
   <cacheFields count="27">
     <cacheField name="Title" numFmtId="0">
@@ -1182,7 +1272,7 @@
       <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
     </cacheField>
     <cacheField name="DATA HORA (Tentativa 1)" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-09-29T17:30:00" maxDate="2026-09-30T11:56:00"/>
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-09-29T17:30:00" maxDate="2026-10-02T09:11:00"/>
     </cacheField>
     <cacheField name="FALAMOS COM (Tentativa 1)" numFmtId="0">
       <sharedItems containsBlank="1"/>
@@ -1193,7 +1283,7 @@
     <cacheField name="DATA HORA (Tentativa 2)" numFmtId="0">
       <sharedItems containsDate="1" containsBlank="1" containsMixedTypes="1" minDate="2026-09-30T12:06:00" maxDate="1899-12-30T00:00:00"/>
     </cacheField>
-    <cacheField name="FALAMOS COM (Tentativa 2)" numFmtId="0">
+    <cacheField name="Campo16" caption="Campo16" numFmtId="0">
       <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
     </cacheField>
     <cacheField name="OBSERVAÇÃO (Tentativa 2)" numFmtId="0">
@@ -1206,7 +1296,7 @@
       <sharedItems containsBlank="1"/>
     </cacheField>
     <cacheField name="OBSERVAÇÃO (Tentativa 3)" numFmtId="0">
-      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
+      <sharedItems containsDate="1" containsBlank="1" containsMixedTypes="1" minDate="2026-10-02T09:15:00" maxDate="2026-10-02T11:36:00"/>
     </cacheField>
     <cacheField name="DATA HORA (Tentativa 4)" numFmtId="0">
       <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
@@ -1255,7 +1345,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Ingrid Geraldo Chaves" refreshedDate="46296.747136226855" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="7" xr:uid="{20ACFB62-B49E-48BD-9B36-3A2C8A7A4B38}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Ingrid Geraldo Chaves" refreshedDate="46297.567664930553" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="7" xr:uid="{20ACFB62-B49E-48BD-9B36-3A2C8A7A4B38}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:Z8" sheet="LIsta de Espera"/>
   </cacheSource>
@@ -1315,7 +1405,7 @@
       <sharedItems containsBlank="1"/>
     </cacheField>
     <cacheField name="OBSERVAÇÃO (Tentativa 2)" numFmtId="0">
-      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
+      <sharedItems containsBlank="1"/>
     </cacheField>
     <cacheField name="DATA HORA (Tentativa 3)" numFmtId="0">
       <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
@@ -1368,7 +1458,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="45">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="46">
   <r>
     <s v="Controle"/>
     <s v="Rio de Janeiro Guia Digital - Imersão Executiva em Saúde Suplementar "/>
@@ -1389,7 +1479,7 @@
     <m/>
     <d v="2026-10-01T09:48:00"/>
     <s v="CAIXA ´POSTAL"/>
-    <m/>
+    <d v="2026-10-02T09:15:00"/>
     <m/>
     <m/>
     <m/>
@@ -1411,7 +1501,7 @@
     <m/>
     <d v="2026-09-29T17:33:00"/>
     <s v="A própria"/>
-    <m/>
+    <s v="confirmado"/>
     <m/>
     <m/>
     <m/>
@@ -1445,7 +1535,7 @@
     <m/>
     <d v="2026-10-01T09:51:00"/>
     <s v="CAIXA POSTAL "/>
-    <m/>
+    <d v="2026-10-02T11:30:00"/>
     <m/>
     <m/>
     <m/>
@@ -1473,7 +1563,7 @@
     <m/>
     <d v="2026-10-01T09:54:00"/>
     <s v="CAIXA POSTAL "/>
-    <m/>
+    <d v="2026-10-02T11:32:00"/>
     <m/>
     <m/>
     <m/>
@@ -1501,7 +1591,7 @@
     <m/>
     <d v="2026-10-01T09:55:00"/>
     <s v="CAIXA POSTAL "/>
-    <m/>
+    <d v="2026-10-02T11:34:00"/>
     <m/>
     <m/>
     <m/>
@@ -1529,7 +1619,7 @@
     <m/>
     <d v="2026-10-01T09:58:00"/>
     <s v="CAIXA POSTAL "/>
-    <m/>
+    <d v="2026-10-02T11:36:00"/>
     <m/>
     <m/>
     <m/>
@@ -1541,7 +1631,7 @@
     <s v="Controle"/>
     <s v="Rio de Janeiro Guia Digital - Imersão Executiva em Saúde Suplementar "/>
     <s v="GSA"/>
-    <x v="0"/>
+    <x v="1"/>
     <s v="RioTrilhos"/>
     <s v="Andressa Urquiza"/>
     <s v="Gerente de Benefícios"/>
@@ -1551,13 +1641,13 @@
     <m/>
     <d v="2026-09-29T17:42:00"/>
     <m/>
-    <s v="Fora de Área/Caixa de Mensagens"/>
+    <s v="confirmado"/>
     <d v="2026-09-30T12:16:00"/>
     <m/>
     <m/>
     <m/>
     <m/>
-    <m/>
+    <d v="2026-10-02T09:44:00"/>
     <m/>
     <m/>
     <m/>
@@ -1585,7 +1675,7 @@
     <m/>
     <m/>
     <m/>
-    <m/>
+    <d v="2026-10-02T09:49:00"/>
     <m/>
     <m/>
     <m/>
@@ -1607,7 +1697,7 @@
     <m/>
     <d v="2026-09-29T17:46:00"/>
     <s v="Confirmado"/>
-    <s v="Confirmado"/>
+    <s v="confirmado"/>
     <s v="confirmou 30/09 ás 12:21"/>
     <m/>
     <m/>
@@ -1635,7 +1725,7 @@
     <m/>
     <d v="2026-09-29T17:48:00"/>
     <s v="Confirmado"/>
-    <s v="Confirmado"/>
+    <s v="confirmado"/>
     <s v="confirmou 30/09 ás 12:23"/>
     <m/>
     <m/>
@@ -1669,7 +1759,7 @@
     <m/>
     <m/>
     <m/>
-    <m/>
+    <d v="2026-10-02T09:54:00"/>
     <m/>
     <m/>
     <m/>
@@ -1718,8 +1808,8 @@
     <m/>
     <m/>
     <d v="2026-09-30T11:56:00"/>
-    <s v="Retornar ás 15:00 hrs"/>
-    <s v="Retornar"/>
+    <s v="Troca de representante "/>
+    <s v="Troca de representante "/>
     <m/>
     <m/>
     <m/>
@@ -1809,7 +1899,7 @@
     <m/>
     <m/>
     <m/>
-    <m/>
+    <d v="2026-10-02T10:00:00"/>
     <m/>
     <m/>
     <m/>
@@ -1821,7 +1911,7 @@
     <s v="Controle"/>
     <s v="Rio de Janeiro Guia Digital - Imersão Executiva em Saúde Suplementar "/>
     <s v="GSA"/>
-    <x v="2"/>
+    <x v="4"/>
     <s v="Equinor"/>
     <s v="Juliana Lopes Vileti"/>
     <s v="Líder de saúde, trabalho e ambiente"/>
@@ -1837,7 +1927,7 @@
     <m/>
     <m/>
     <m/>
-    <m/>
+    <s v="Não tem interesse 02//10/26"/>
     <m/>
     <m/>
     <m/>
@@ -1849,7 +1939,7 @@
     <s v="Controle"/>
     <s v="Rio de Janeiro Guia Digital - Imersão Executiva em Saúde Suplementar "/>
     <s v="GSA"/>
-    <x v="2"/>
+    <x v="1"/>
     <s v="SAÚDE PETROBRAS"/>
     <s v="Carolina Rocha Campos Pires"/>
     <s v="Gerente de RH"/>
@@ -1859,13 +1949,13 @@
     <m/>
     <d v="2026-09-30T10:05:00"/>
     <m/>
-    <s v="Não atende/Ocupado"/>
+    <s v="confirmado"/>
     <d v="2026-09-30T12:43:00"/>
     <m/>
     <m/>
     <m/>
     <m/>
-    <m/>
+    <s v="Confirmou 02/10 ás 10:16"/>
     <m/>
     <m/>
     <m/>
@@ -1893,7 +1983,7 @@
     <m/>
     <m/>
     <m/>
-    <m/>
+    <d v="2026-10-02T10:23:00"/>
     <m/>
     <m/>
     <m/>
@@ -1921,7 +2011,7 @@
     <m/>
     <m/>
     <m/>
-    <m/>
+    <d v="2026-10-02T10:31:00"/>
     <m/>
     <m/>
     <m/>
@@ -1943,7 +2033,7 @@
     <m/>
     <d v="2026-09-30T10:10:00"/>
     <s v="A própria "/>
-    <s v="Confirmado"/>
+    <s v="confirmado"/>
     <s v="confirmou 30/09 ás 13:00"/>
     <m/>
     <m/>
@@ -1977,7 +2067,7 @@
     <m/>
     <m/>
     <m/>
-    <m/>
+    <d v="2026-10-02T10:33:00"/>
     <m/>
     <m/>
     <m/>
@@ -2005,7 +2095,7 @@
     <m/>
     <m/>
     <m/>
-    <m/>
+    <d v="2026-10-02T10:38:00"/>
     <m/>
     <m/>
     <m/>
@@ -2083,7 +2173,7 @@
     <m/>
     <d v="2026-09-30T10:22:00"/>
     <s v="O próprio "/>
-    <s v="Confirmado"/>
+    <s v="confirmado"/>
     <s v="Confirmou 30/09 ás 15:20"/>
     <m/>
     <m/>
@@ -2117,7 +2207,7 @@
     <m/>
     <m/>
     <m/>
-    <m/>
+    <d v="2026-10-02T10:52:00"/>
     <m/>
     <m/>
     <m/>
@@ -2139,7 +2229,7 @@
     <m/>
     <d v="2026-09-30T00:00:00"/>
     <s v="O próprio"/>
-    <s v="Confirmado"/>
+    <s v="confirmado"/>
     <m/>
     <m/>
     <m/>
@@ -2173,7 +2263,7 @@
     <m/>
     <m/>
     <m/>
-    <m/>
+    <d v="2026-10-02T10:54:00"/>
     <m/>
     <m/>
     <m/>
@@ -2201,7 +2291,7 @@
     <m/>
     <m/>
     <m/>
-    <m/>
+    <d v="2026-10-02T10:57:00"/>
     <m/>
     <m/>
     <m/>
@@ -2223,7 +2313,7 @@
     <m/>
     <d v="2026-09-30T10:32:00"/>
     <m/>
-    <s v="Não atende/Ocupado"/>
+    <s v="confirmado"/>
     <n v="46295.65902777778"/>
     <m/>
     <m/>
@@ -2257,7 +2347,7 @@
     <m/>
     <m/>
     <m/>
-    <m/>
+    <d v="2026-10-02T10:59:00"/>
     <m/>
     <m/>
     <m/>
@@ -2279,7 +2369,7 @@
     <m/>
     <d v="2026-09-30T00:00:00"/>
     <s v="O próprio"/>
-    <s v="Confirmado"/>
+    <s v="confirmado"/>
     <s v="Confirmou 30/09 ás 15:53"/>
     <m/>
     <m/>
@@ -2307,7 +2397,7 @@
     <m/>
     <d v="2026-09-30T00:00:00"/>
     <s v="O próprio"/>
-    <s v="Confirmado"/>
+    <s v="confirmado"/>
     <s v="Confirmou 30/09 ás 15:54"/>
     <m/>
     <m/>
@@ -2335,7 +2425,7 @@
     <m/>
     <d v="2026-09-30T10:40:00"/>
     <s v="O próprio"/>
-    <s v="Confirmado"/>
+    <s v="confirmado"/>
     <s v="Confirmou 30/09 ás 15:55"/>
     <m/>
     <m/>
@@ -2363,7 +2453,7 @@
     <m/>
     <d v="2026-09-30T00:00:00"/>
     <s v="O próprio"/>
-    <s v="Confirmado"/>
+    <s v="confirmado"/>
     <s v="Confirmou 30/09 ás 15:58"/>
     <m/>
     <m/>
@@ -2397,7 +2487,7 @@
     <m/>
     <m/>
     <m/>
-    <m/>
+    <d v="2026-10-02T11:07:00"/>
     <m/>
     <m/>
     <m/>
@@ -2425,7 +2515,7 @@
     <m/>
     <m/>
     <m/>
-    <m/>
+    <d v="2026-10-02T11:09:00"/>
     <m/>
     <m/>
     <m/>
@@ -2453,7 +2543,7 @@
     <m/>
     <m/>
     <m/>
-    <m/>
+    <d v="2026-10-02T11:11:00"/>
     <m/>
     <m/>
     <m/>
@@ -2465,7 +2555,7 @@
     <s v="Controle"/>
     <s v="Rio de Janeiro Guia Digital - Imersão Executiva em Saúde Suplementar "/>
     <s v="GSA"/>
-    <x v="0"/>
+    <x v="1"/>
     <s v="SISTEMA FIRJAN"/>
     <s v="LAURENT CARVALHO MARQUES"/>
     <s v="COORDENADOR DE PERFORMANCE E REMUNERAÇÃO"/>
@@ -2481,7 +2571,7 @@
     <m/>
     <m/>
     <m/>
-    <m/>
+    <s v="confirmou 02/10 ás 11:16"/>
     <m/>
     <m/>
     <m/>
@@ -2503,7 +2593,7 @@
     <m/>
     <d v="2026-09-30T11:10:00"/>
     <s v="O próprio "/>
-    <s v="Confirmado"/>
+    <s v="confirmado"/>
     <s v="Confirmou 30/09 ás 16:10"/>
     <m/>
     <m/>
@@ -2521,7 +2611,7 @@
     <s v="Controle"/>
     <s v="Rio de Janeiro Guia Digital - Imersão Executiva em Saúde Suplementar "/>
     <s v="GSA"/>
-    <x v="0"/>
+    <x v="1"/>
     <s v="Constellation"/>
     <s v="Távira Tavares"/>
     <s v="Coordenadora médica do trabalho"/>
@@ -2537,7 +2627,7 @@
     <m/>
     <m/>
     <m/>
-    <m/>
+    <s v="confirmou 02/10 ás 11:19"/>
     <m/>
     <m/>
     <m/>
@@ -2559,7 +2649,7 @@
     <m/>
     <d v="2026-09-30T11:30:00"/>
     <s v="A própria "/>
-    <s v="Confirmado"/>
+    <s v="confirmado"/>
     <s v="Confirmou ás 16:15"/>
     <m/>
     <m/>
@@ -2593,7 +2683,7 @@
     <m/>
     <m/>
     <m/>
-    <m/>
+    <d v="2026-10-02T11:26:00"/>
     <m/>
     <m/>
     <m/>
@@ -2617,6 +2707,34 @@
     <m/>
     <s v="Fora de Área/Caixa de Mensagens"/>
     <d v="2026-09-30T16:19:00"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <d v="2026-10-02T11:28:00"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="Controle"/>
+    <s v="Rio de Janeiro Guia Digital - Imersão Executiva em Saúde Suplementar "/>
+    <s v="GSA"/>
+    <x v="1"/>
+    <s v="TRANSPETRO"/>
+    <s v="Leandro Ribeiro Quintanilha"/>
+    <s v="Enfermeiro do Trabalho"/>
+    <s v="21 99842-8835"/>
+    <s v="leandroquintanilha@transpetro.com.br"/>
+    <m/>
+    <m/>
+    <d v="2026-10-02T09:11:00"/>
+    <s v="O próprio"/>
+    <m/>
+    <m/>
     <m/>
     <m/>
     <m/>
@@ -2679,7 +2797,7 @@
     <m/>
     <s v="3° Tentativa 01/10 16:56"/>
     <s v="Caixa postal"/>
-    <m/>
+    <s v="4° Tentativa 02/10 10:40"/>
     <m/>
     <m/>
     <m/>
@@ -2735,7 +2853,7 @@
     <m/>
     <s v="3° Tentativa 01/16:57"/>
     <s v="Caixa postal"/>
-    <m/>
+    <s v="4° Tentativa 02/10 10:42"/>
     <m/>
     <m/>
     <m/>
@@ -2834,7 +2952,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B05C194E-490D-4E1B-B19B-47ED60C72B4E}" name="Tabela dinâmica4" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Status">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B05C194E-490D-4E1B-B19B-47ED60C72B4E}" name="Tabela dinâmica4" cacheId="24" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Status">
   <location ref="E3:F9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="27">
     <pivotField showAll="0"/>
@@ -2922,7 +3040,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3817860A-E9BE-4B15-8F81-AA3D911F543B}" name="Tabela dinâmica2" cacheId="13" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Status">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F7F21FCA-C5E3-4E23-90FD-385B589D9798}" name="Tabela dinâmica2" cacheId="20" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Status">
   <location ref="B3:C11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="27">
     <pivotField showAll="0"/>
@@ -2931,12 +3049,12 @@
     <pivotField axis="axisRow" dataField="1" showAll="0">
       <items count="8">
         <item sd="0" x="1"/>
-        <item x="0"/>
-        <item x="2"/>
+        <item sd="0" x="0"/>
+        <item sd="0" x="2"/>
         <item m="1" x="5"/>
         <item m="1" x="6"/>
-        <item x="3"/>
-        <item x="4"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="4"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -3222,21 +3340,21 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
-    <col min="2" max="2" width="33.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.77734375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8.109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B2" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C2" s="7"/>
       <c r="E2" s="7" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F2" s="7"/>
     </row>
@@ -3258,13 +3376,13 @@
       <c r="B4" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="C4" s="40">
-        <v>19</v>
+      <c r="C4" s="46">
+        <v>25</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="F4" s="40">
+      <c r="F4" s="46">
         <v>5</v>
       </c>
     </row>
@@ -3272,13 +3390,13 @@
       <c r="B5" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C5" s="40">
-        <v>16</v>
+      <c r="C5" s="46">
+        <v>21</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="F5" s="40">
+      <c r="F5" s="46">
         <v>4</v>
       </c>
     </row>
@@ -3286,13 +3404,13 @@
       <c r="B6" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="C6" s="40">
+      <c r="C6" s="46">
         <v>1</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>242</v>
       </c>
-      <c r="F6" s="40">
+      <c r="F6" s="46">
         <v>1</v>
       </c>
     </row>
@@ -3300,13 +3418,13 @@
       <c r="B7" s="6" t="s">
         <v>242</v>
       </c>
-      <c r="C7" s="40">
-        <v>2</v>
+      <c r="C7" s="46">
+        <v>3</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="F7" s="40">
+      <c r="F7" s="46">
         <v>2</v>
       </c>
     </row>
@@ -3314,13 +3432,13 @@
       <c r="B8" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="C8" s="40">
-        <v>26</v>
+      <c r="C8" s="46">
+        <v>21</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>240</v>
       </c>
-      <c r="F8" s="40">
+      <c r="F8" s="46">
         <v>2</v>
       </c>
     </row>
@@ -3328,13 +3446,13 @@
       <c r="B9" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="40">
-        <v>14</v>
+      <c r="C9" s="46">
+        <v>11</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="F9" s="40">
+      <c r="F9" s="46">
         <v>7</v>
       </c>
     </row>
@@ -3342,16 +3460,16 @@
       <c r="B10" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="C10" s="40">
-        <v>12</v>
+      <c r="C10" s="46">
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B11" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="C11" s="40">
-        <v>45</v>
+      <c r="C11" s="46">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -3360,6 +3478,336 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A10D502-E2BD-4280-8BEE-FB1DC65D0D74}">
+  <dimension ref="B2:D32"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="47.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="45.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B2" s="47" t="s">
+        <v>291</v>
+      </c>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+    </row>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B3" s="48" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="48" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="48" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B4" s="49" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" s="49" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="49" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B5" s="49" t="s">
+        <v>82</v>
+      </c>
+      <c r="C5" s="49" t="s">
+        <v>83</v>
+      </c>
+      <c r="D5" s="49" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B6" s="49" t="s">
+        <v>92</v>
+      </c>
+      <c r="C6" s="49" t="s">
+        <v>93</v>
+      </c>
+      <c r="D6" s="49" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B7" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="C7" s="51" t="s">
+        <v>98</v>
+      </c>
+      <c r="D7" s="49" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B8" s="49" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="49" t="s">
+        <v>105</v>
+      </c>
+      <c r="D8" s="49" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B9" s="49" t="s">
+        <v>117</v>
+      </c>
+      <c r="C9" s="49" t="s">
+        <v>118</v>
+      </c>
+      <c r="D9" s="49" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B10" s="49" t="s">
+        <v>127</v>
+      </c>
+      <c r="C10" s="49" t="s">
+        <v>128</v>
+      </c>
+      <c r="D10" s="49" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B11" s="49" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" s="49" t="s">
+        <v>139</v>
+      </c>
+      <c r="D11" s="49" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B12" s="49" t="s">
+        <v>149</v>
+      </c>
+      <c r="C12" s="49" t="s">
+        <v>150</v>
+      </c>
+      <c r="D12" s="49" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B13" s="49" t="s">
+        <v>156</v>
+      </c>
+      <c r="C13" s="49" t="s">
+        <v>157</v>
+      </c>
+      <c r="D13" s="49" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B14" s="49" t="s">
+        <v>164</v>
+      </c>
+      <c r="C14" s="49" t="s">
+        <v>165</v>
+      </c>
+      <c r="D14" s="49" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B15" s="49" t="s">
+        <v>176</v>
+      </c>
+      <c r="C15" s="49" t="s">
+        <v>177</v>
+      </c>
+      <c r="D15" s="49" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B16" s="49" t="s">
+        <v>183</v>
+      </c>
+      <c r="C16" s="49" t="s">
+        <v>184</v>
+      </c>
+      <c r="D16" s="49" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B17" s="49" t="s">
+        <v>187</v>
+      </c>
+      <c r="C17" s="49" t="s">
+        <v>188</v>
+      </c>
+      <c r="D17" s="49" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B18" s="49" t="s">
+        <v>191</v>
+      </c>
+      <c r="C18" s="49" t="s">
+        <v>192</v>
+      </c>
+      <c r="D18" s="49" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B19" s="49" t="s">
+        <v>191</v>
+      </c>
+      <c r="C19" s="49" t="s">
+        <v>195</v>
+      </c>
+      <c r="D19" s="49" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B20" s="49" t="s">
+        <v>210</v>
+      </c>
+      <c r="C20" s="49" t="s">
+        <v>211</v>
+      </c>
+      <c r="D20" s="49" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B21" s="49" t="s">
+        <v>210</v>
+      </c>
+      <c r="C21" s="49" t="s">
+        <v>214</v>
+      </c>
+      <c r="D21" s="49" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B22" s="49" t="s">
+        <v>74</v>
+      </c>
+      <c r="C22" s="49" t="s">
+        <v>217</v>
+      </c>
+      <c r="D22" s="49" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B23" s="49" t="s">
+        <v>220</v>
+      </c>
+      <c r="C23" s="49" t="s">
+        <v>221</v>
+      </c>
+      <c r="D23" s="49" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B24" s="49" t="s">
+        <v>278</v>
+      </c>
+      <c r="C24" s="49" t="s">
+        <v>279</v>
+      </c>
+      <c r="D24" s="49" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="27" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B27" s="47" t="s">
+        <v>292</v>
+      </c>
+      <c r="C27" s="47"/>
+      <c r="D27" s="47"/>
+    </row>
+    <row r="28" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B28" s="48" t="s">
+        <v>4</v>
+      </c>
+      <c r="C28" s="48" t="s">
+        <v>5</v>
+      </c>
+      <c r="D28" s="48" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B29" s="49" t="s">
+        <v>31</v>
+      </c>
+      <c r="C29" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="D29" s="49" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="30" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B30" s="49" t="s">
+        <v>66</v>
+      </c>
+      <c r="C30" s="49" t="s">
+        <v>67</v>
+      </c>
+      <c r="D30" s="49" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="31" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B31" s="49" t="s">
+        <v>66</v>
+      </c>
+      <c r="C31" s="49" t="s">
+        <v>76</v>
+      </c>
+      <c r="D31" s="49" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B32" s="49" t="s">
+        <v>66</v>
+      </c>
+      <c r="C32" s="49" t="s">
+        <v>90</v>
+      </c>
+      <c r="D32" s="49" t="s">
+        <v>91</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B27:D27"/>
+  </mergeCells>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Z1000"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -3438,9 +3886,7 @@
       <c r="O1" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="9" t="s">
-        <v>15</v>
-      </c>
+      <c r="P1" s="9"/>
       <c r="Q1" s="9" t="s">
         <v>16</v>
       </c>
@@ -3514,13 +3960,15 @@
       </c>
       <c r="P2" s="11"/>
       <c r="Q2" s="11"/>
-      <c r="R2" s="38">
+      <c r="R2" s="15">
         <v>46296.408333333333</v>
       </c>
-      <c r="S2" s="11" t="s">
-        <v>277</v>
-      </c>
-      <c r="T2" s="11"/>
+      <c r="S2" s="13" t="s">
+        <v>276</v>
+      </c>
+      <c r="T2" s="15">
+        <v>46297.385416666664</v>
+      </c>
       <c r="U2" s="11"/>
       <c r="V2" s="11"/>
       <c r="W2" s="11"/>
@@ -3564,13 +4012,15 @@
       <c r="M3" s="18" t="s">
         <v>229</v>
       </c>
-      <c r="N3" s="16"/>
+      <c r="N3" s="18" t="s">
+        <v>283</v>
+      </c>
       <c r="O3" s="16"/>
       <c r="P3" s="16"/>
-      <c r="Q3" s="11"/>
-      <c r="R3" s="11"/>
-      <c r="S3" s="11"/>
-      <c r="T3" s="11"/>
+      <c r="Q3" s="16"/>
+      <c r="R3" s="16"/>
+      <c r="S3" s="16"/>
+      <c r="T3" s="16"/>
       <c r="U3" s="11"/>
       <c r="V3" s="11"/>
       <c r="W3" s="11"/>
@@ -3620,13 +4070,15 @@
       </c>
       <c r="P4" s="11"/>
       <c r="Q4" s="11"/>
-      <c r="R4" s="38">
+      <c r="R4" s="15">
         <v>46296.410416666666</v>
       </c>
-      <c r="S4" s="11" t="s">
-        <v>278</v>
-      </c>
-      <c r="T4" s="11"/>
+      <c r="S4" s="13" t="s">
+        <v>277</v>
+      </c>
+      <c r="T4" s="15">
+        <v>46297.479166666664</v>
+      </c>
       <c r="U4" s="11"/>
       <c r="V4" s="11"/>
       <c r="W4" s="11"/>
@@ -3676,13 +4128,15 @@
       </c>
       <c r="P5" s="11"/>
       <c r="Q5" s="11"/>
-      <c r="R5" s="38">
+      <c r="R5" s="15">
         <v>46296.412499999999</v>
       </c>
-      <c r="S5" s="11" t="s">
-        <v>278</v>
-      </c>
-      <c r="T5" s="11"/>
+      <c r="S5" s="13" t="s">
+        <v>277</v>
+      </c>
+      <c r="T5" s="15">
+        <v>46297.480555555558</v>
+      </c>
       <c r="U5" s="11"/>
       <c r="V5" s="11"/>
       <c r="W5" s="11"/>
@@ -3732,13 +4186,15 @@
       </c>
       <c r="P6" s="11"/>
       <c r="Q6" s="11"/>
-      <c r="R6" s="38">
+      <c r="R6" s="15">
         <v>46296.413194444445</v>
       </c>
-      <c r="S6" s="11" t="s">
-        <v>278</v>
-      </c>
-      <c r="T6" s="11"/>
+      <c r="S6" s="13" t="s">
+        <v>277</v>
+      </c>
+      <c r="T6" s="15">
+        <v>46297.481944444444</v>
+      </c>
       <c r="U6" s="11"/>
       <c r="V6" s="11"/>
       <c r="W6" s="11"/>
@@ -3788,13 +4244,15 @@
       </c>
       <c r="P7" s="11"/>
       <c r="Q7" s="11"/>
-      <c r="R7" s="38">
+      <c r="R7" s="15">
         <v>46296.415277777778</v>
       </c>
-      <c r="S7" s="11" t="s">
-        <v>278</v>
-      </c>
-      <c r="T7" s="11"/>
+      <c r="S7" s="13" t="s">
+        <v>277</v>
+      </c>
+      <c r="T7" s="15">
+        <v>46297.48333333333</v>
+      </c>
       <c r="U7" s="11"/>
       <c r="V7" s="11"/>
       <c r="W7" s="11"/>
@@ -3803,50 +4261,52 @@
       <c r="Z7" s="11"/>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="E8" s="11" t="s">
+      <c r="D8" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="E8" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="F8" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="G8" s="11" t="s">
+      <c r="G8" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="H8" s="14">
+      <c r="H8" s="23">
         <v>21999915569</v>
       </c>
-      <c r="I8" s="12" t="s">
+      <c r="I8" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="J8" s="11"/>
-      <c r="K8" s="11"/>
-      <c r="L8" s="15">
+      <c r="J8" s="16"/>
+      <c r="K8" s="16"/>
+      <c r="L8" s="19">
         <v>46294.737500000003</v>
       </c>
-      <c r="M8" s="13"/>
-      <c r="N8" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="O8" s="15">
+      <c r="M8" s="18"/>
+      <c r="N8" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="O8" s="19">
         <v>46295.511111111111</v>
       </c>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
+      <c r="P8" s="16"/>
+      <c r="Q8" s="16"/>
+      <c r="R8" s="16"/>
+      <c r="S8" s="16"/>
+      <c r="T8" s="19">
+        <v>46297.405555555553</v>
+      </c>
       <c r="U8" s="11"/>
       <c r="V8" s="11"/>
       <c r="W8" s="11"/>
@@ -3898,7 +4358,9 @@
       <c r="Q9" s="11"/>
       <c r="R9" s="11"/>
       <c r="S9" s="11"/>
-      <c r="T9" s="11"/>
+      <c r="T9" s="15">
+        <v>46297.40902777778</v>
+      </c>
       <c r="U9" s="11"/>
       <c r="V9" s="11"/>
       <c r="W9" s="11"/>
@@ -3949,10 +4411,10 @@
         <v>251</v>
       </c>
       <c r="P10" s="16"/>
-      <c r="Q10" s="11"/>
-      <c r="R10" s="11"/>
-      <c r="S10" s="11"/>
-      <c r="T10" s="11"/>
+      <c r="Q10" s="16"/>
+      <c r="R10" s="16"/>
+      <c r="S10" s="16"/>
+      <c r="T10" s="16"/>
       <c r="U10" s="11"/>
       <c r="V10" s="11"/>
       <c r="W10" s="11"/>
@@ -4003,10 +4465,10 @@
         <v>252</v>
       </c>
       <c r="P11" s="16"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
-      <c r="S11" s="11"/>
-      <c r="T11" s="11"/>
+      <c r="Q11" s="16"/>
+      <c r="R11" s="16"/>
+      <c r="S11" s="16"/>
+      <c r="T11" s="16"/>
       <c r="U11" s="11"/>
       <c r="V11" s="11"/>
       <c r="W11" s="11"/>
@@ -4058,7 +4520,9 @@
       <c r="Q12" s="11"/>
       <c r="R12" s="11"/>
       <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
+      <c r="T12" s="15">
+        <v>46297.412499999999</v>
+      </c>
       <c r="U12" s="11"/>
       <c r="V12" s="11"/>
       <c r="W12" s="11"/>
@@ -4067,50 +4531,50 @@
       <c r="Z12" s="11"/>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="D13" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="E13" s="11" t="s">
+      <c r="E13" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="F13" s="11" t="s">
+      <c r="F13" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="G13" s="11" t="s">
+      <c r="G13" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="H13" s="14">
+      <c r="H13" s="17">
         <v>21975163913</v>
       </c>
-      <c r="I13" s="12" t="s">
+      <c r="I13" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="J13" s="11"/>
-      <c r="K13" s="11"/>
-      <c r="L13" s="15">
+      <c r="J13" s="16"/>
+      <c r="K13" s="16"/>
+      <c r="L13" s="19">
         <v>46294.744444444441</v>
       </c>
-      <c r="M13" s="13"/>
-      <c r="N13" s="13" t="s">
+      <c r="M13" s="18"/>
+      <c r="N13" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="O13" s="13">
+      <c r="O13" s="16">
         <v>46295.519444444442</v>
       </c>
-      <c r="P13" s="11"/>
-      <c r="Q13" s="11"/>
-      <c r="R13" s="11"/>
-      <c r="S13" s="11"/>
-      <c r="T13" s="11"/>
+      <c r="P13" s="16"/>
+      <c r="Q13" s="16"/>
+      <c r="R13" s="16"/>
+      <c r="S13" s="16"/>
+      <c r="T13" s="16"/>
       <c r="U13" s="11"/>
       <c r="V13" s="11"/>
       <c r="W13" s="11"/>
@@ -4119,50 +4583,50 @@
       <c r="Z13" s="11"/>
     </row>
     <row r="14" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="D14" s="13" t="s">
+      <c r="D14" s="40" t="s">
         <v>253</v>
       </c>
-      <c r="E14" s="11" t="s">
+      <c r="E14" s="38" t="s">
         <v>109</v>
       </c>
-      <c r="F14" s="11" t="s">
+      <c r="F14" s="38" t="s">
         <v>110</v>
       </c>
-      <c r="G14" s="11" t="s">
+      <c r="G14" s="38" t="s">
         <v>111</v>
       </c>
-      <c r="H14" s="14">
+      <c r="H14" s="41">
         <v>21979163663</v>
       </c>
-      <c r="I14" s="12" t="s">
+      <c r="I14" s="39" t="s">
         <v>112</v>
       </c>
-      <c r="J14" s="11"/>
-      <c r="K14" s="11"/>
-      <c r="L14" s="15">
+      <c r="J14" s="38"/>
+      <c r="K14" s="38"/>
+      <c r="L14" s="42">
         <v>46295.49722222222</v>
       </c>
-      <c r="M14" s="13" t="s">
-        <v>254</v>
-      </c>
-      <c r="N14" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="O14" s="11"/>
-      <c r="P14" s="11"/>
-      <c r="Q14" s="11"/>
-      <c r="R14" s="11"/>
-      <c r="S14" s="11"/>
-      <c r="T14" s="11"/>
+      <c r="M14" s="40" t="s">
+        <v>284</v>
+      </c>
+      <c r="N14" s="40" t="s">
+        <v>284</v>
+      </c>
+      <c r="O14" s="38"/>
+      <c r="P14" s="38"/>
+      <c r="Q14" s="38"/>
+      <c r="R14" s="38"/>
+      <c r="S14" s="38"/>
+      <c r="T14" s="38"/>
       <c r="U14" s="11"/>
       <c r="V14" s="11"/>
       <c r="W14" s="11"/>
@@ -4205,7 +4669,7 @@
       </c>
       <c r="M15" s="27"/>
       <c r="N15" s="27" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="O15" s="29">
         <v>46295.522916666669</v>
@@ -4214,7 +4678,7 @@
       <c r="Q15" s="25"/>
       <c r="R15" s="25"/>
       <c r="S15" s="25"/>
-      <c r="T15" s="11"/>
+      <c r="T15" s="25"/>
       <c r="U15" s="11"/>
       <c r="V15" s="11"/>
       <c r="W15" s="11"/>
@@ -4261,10 +4725,10 @@
       <c r="N16" s="16"/>
       <c r="O16" s="16"/>
       <c r="P16" s="16"/>
-      <c r="Q16" s="11"/>
-      <c r="R16" s="11"/>
-      <c r="S16" s="11"/>
-      <c r="T16" s="11"/>
+      <c r="Q16" s="16"/>
+      <c r="R16" s="16"/>
+      <c r="S16" s="16"/>
+      <c r="T16" s="16"/>
       <c r="U16" s="11"/>
       <c r="V16" s="11"/>
       <c r="W16" s="11"/>
@@ -4316,7 +4780,9 @@
       <c r="Q17" s="11"/>
       <c r="R17" s="11"/>
       <c r="S17" s="11"/>
-      <c r="T17" s="11"/>
+      <c r="T17" s="15">
+        <v>46297.416666666664</v>
+      </c>
       <c r="U17" s="11"/>
       <c r="V17" s="11"/>
       <c r="W17" s="11"/>
@@ -4325,50 +4791,52 @@
       <c r="Z17" s="11"/>
     </row>
     <row r="18" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="11" t="s">
+      <c r="A18" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="11" t="s">
+      <c r="B18" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="C18" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="D18" s="13" t="s">
+      <c r="D18" s="27" t="s">
+        <v>242</v>
+      </c>
+      <c r="E18" s="25" t="s">
+        <v>120</v>
+      </c>
+      <c r="F18" s="25" t="s">
+        <v>124</v>
+      </c>
+      <c r="G18" s="25" t="s">
+        <v>125</v>
+      </c>
+      <c r="H18" s="28">
+        <v>21972822205</v>
+      </c>
+      <c r="I18" s="26" t="s">
+        <v>126</v>
+      </c>
+      <c r="J18" s="25"/>
+      <c r="K18" s="25"/>
+      <c r="L18" s="29">
+        <v>46295.419444444444</v>
+      </c>
+      <c r="M18" s="25"/>
+      <c r="N18" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="E18" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="F18" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="G18" s="11" t="s">
-        <v>125</v>
-      </c>
-      <c r="H18" s="14">
-        <v>21972822205</v>
-      </c>
-      <c r="I18" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="J18" s="11"/>
-      <c r="K18" s="11"/>
-      <c r="L18" s="15">
-        <v>46295.419444444444</v>
-      </c>
-      <c r="M18" s="11"/>
-      <c r="N18" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="O18" s="15">
+      <c r="O18" s="29">
         <v>46295.52847222222</v>
       </c>
-      <c r="P18" s="11"/>
-      <c r="Q18" s="11"/>
-      <c r="R18" s="11"/>
-      <c r="S18" s="11"/>
-      <c r="T18" s="11"/>
+      <c r="P18" s="25"/>
+      <c r="Q18" s="25"/>
+      <c r="R18" s="25"/>
+      <c r="S18" s="25"/>
+      <c r="T18" s="27" t="s">
+        <v>285</v>
+      </c>
       <c r="U18" s="11"/>
       <c r="V18" s="11"/>
       <c r="W18" s="11"/>
@@ -4377,50 +4845,52 @@
       <c r="Z18" s="11"/>
     </row>
     <row r="19" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="11" t="s">
+      <c r="A19" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="B19" s="11" t="s">
+      <c r="B19" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="C19" s="12" t="s">
+      <c r="C19" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="D19" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="E19" s="11" t="s">
+      <c r="D19" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="E19" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="F19" s="11" t="s">
+      <c r="F19" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="G19" s="11" t="s">
+      <c r="G19" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="H19" s="14">
+      <c r="H19" s="23">
         <v>21994270849</v>
       </c>
-      <c r="I19" s="12" t="s">
+      <c r="I19" s="17" t="s">
         <v>130</v>
       </c>
-      <c r="J19" s="11"/>
-      <c r="K19" s="11"/>
-      <c r="L19" s="15">
+      <c r="J19" s="16"/>
+      <c r="K19" s="16"/>
+      <c r="L19" s="19">
         <v>46295.420138888891</v>
       </c>
-      <c r="M19" s="11"/>
-      <c r="N19" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="O19" s="15">
+      <c r="M19" s="16"/>
+      <c r="N19" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="O19" s="19">
         <v>46295.529861111114</v>
       </c>
-      <c r="P19" s="11"/>
-      <c r="Q19" s="11"/>
-      <c r="R19" s="11"/>
-      <c r="S19" s="11"/>
-      <c r="T19" s="11"/>
+      <c r="P19" s="16"/>
+      <c r="Q19" s="16"/>
+      <c r="R19" s="16"/>
+      <c r="S19" s="16"/>
+      <c r="T19" s="18" t="s">
+        <v>286</v>
+      </c>
       <c r="U19" s="11"/>
       <c r="V19" s="11"/>
       <c r="W19" s="11"/>
@@ -4472,7 +4942,9 @@
       <c r="Q20" s="11"/>
       <c r="R20" s="11"/>
       <c r="S20" s="11"/>
-      <c r="T20" s="11"/>
+      <c r="T20" s="15">
+        <v>46297.432638888888</v>
+      </c>
       <c r="U20" s="11"/>
       <c r="V20" s="11"/>
       <c r="W20" s="11"/>
@@ -4524,7 +4996,9 @@
       <c r="Q21" s="11"/>
       <c r="R21" s="11"/>
       <c r="S21" s="11"/>
-      <c r="T21" s="11"/>
+      <c r="T21" s="15">
+        <v>46297.438194444447</v>
+      </c>
       <c r="U21" s="11"/>
       <c r="V21" s="11"/>
       <c r="W21" s="11"/>
@@ -4566,19 +5040,19 @@
         <v>46295.423611111109</v>
       </c>
       <c r="M22" s="18" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="N22" s="18" t="s">
         <v>39</v>
       </c>
       <c r="O22" s="18" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="P22" s="16"/>
-      <c r="Q22" s="11"/>
-      <c r="R22" s="11"/>
-      <c r="S22" s="11"/>
-      <c r="T22" s="11"/>
+      <c r="Q22" s="16"/>
+      <c r="R22" s="16"/>
+      <c r="S22" s="16"/>
+      <c r="T22" s="16"/>
       <c r="U22" s="11"/>
       <c r="V22" s="11"/>
       <c r="W22" s="11"/>
@@ -4630,7 +5104,9 @@
       <c r="Q23" s="11"/>
       <c r="R23" s="11"/>
       <c r="S23" s="11"/>
-      <c r="T23" s="11"/>
+      <c r="T23" s="15">
+        <v>46297.439583333333</v>
+      </c>
       <c r="U23" s="11"/>
       <c r="V23" s="11"/>
       <c r="W23" s="11"/>
@@ -4682,7 +5158,9 @@
       <c r="Q24" s="11"/>
       <c r="R24" s="11"/>
       <c r="S24" s="11"/>
-      <c r="T24" s="11"/>
+      <c r="T24" s="15">
+        <v>46297.443055555559</v>
+      </c>
       <c r="U24" s="11"/>
       <c r="V24" s="11"/>
       <c r="W24" s="11"/>
@@ -4691,50 +5169,50 @@
       <c r="Z24" s="11"/>
     </row>
     <row r="25" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="11" t="s">
+      <c r="A25" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="B25" s="11" t="s">
+      <c r="B25" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="C25" s="12" t="s">
+      <c r="C25" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="D25" s="13" t="s">
+      <c r="D25" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="E25" s="11" t="s">
+      <c r="E25" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="F25" s="11" t="s">
+      <c r="F25" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="G25" s="11" t="s">
+      <c r="G25" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="H25" s="14">
+      <c r="H25" s="17">
         <v>21988010202</v>
       </c>
-      <c r="I25" s="12" t="s">
+      <c r="I25" s="17" t="s">
         <v>152</v>
       </c>
-      <c r="J25" s="11"/>
-      <c r="K25" s="11"/>
-      <c r="L25" s="15">
+      <c r="J25" s="16"/>
+      <c r="K25" s="16"/>
+      <c r="L25" s="19">
         <v>46295.426388888889</v>
       </c>
-      <c r="M25" s="11"/>
-      <c r="N25" s="13" t="s">
+      <c r="M25" s="18"/>
+      <c r="N25" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="O25" s="13">
+      <c r="O25" s="16">
         <v>46295.582638888889</v>
       </c>
-      <c r="P25" s="11"/>
-      <c r="Q25" s="11"/>
-      <c r="R25" s="11"/>
-      <c r="S25" s="11"/>
-      <c r="T25" s="11"/>
+      <c r="P25" s="16"/>
+      <c r="Q25" s="16"/>
+      <c r="R25" s="16"/>
+      <c r="S25" s="16"/>
+      <c r="T25" s="16"/>
       <c r="U25" s="11"/>
       <c r="V25" s="11"/>
       <c r="W25" s="11"/>
@@ -4776,19 +5254,19 @@
         <v>46295.430555555555</v>
       </c>
       <c r="M26" s="27" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N26" s="27" t="s">
         <v>242</v>
       </c>
       <c r="O26" s="27" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="P26" s="25"/>
       <c r="Q26" s="25"/>
-      <c r="R26" s="11"/>
-      <c r="S26" s="11"/>
-      <c r="T26" s="11"/>
+      <c r="R26" s="25"/>
+      <c r="S26" s="25"/>
+      <c r="T26" s="25"/>
       <c r="U26" s="11"/>
       <c r="V26" s="11"/>
       <c r="W26" s="11"/>
@@ -4830,19 +5308,19 @@
         <v>46295.431944444441</v>
       </c>
       <c r="M27" s="18" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="N27" s="18" t="s">
         <v>39</v>
       </c>
       <c r="O27" s="18" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="P27" s="16"/>
       <c r="Q27" s="16"/>
       <c r="R27" s="16"/>
       <c r="S27" s="16"/>
-      <c r="T27" s="11"/>
+      <c r="T27" s="16"/>
       <c r="U27" s="11"/>
       <c r="V27" s="11"/>
       <c r="W27" s="11"/>
@@ -4894,7 +5372,9 @@
       <c r="Q28" s="11"/>
       <c r="R28" s="11"/>
       <c r="S28" s="11"/>
-      <c r="T28" s="11"/>
+      <c r="T28" s="15">
+        <v>46297.452777777777</v>
+      </c>
       <c r="U28" s="11"/>
       <c r="V28" s="11"/>
       <c r="W28" s="11"/>
@@ -4943,10 +5423,10 @@
       </c>
       <c r="O29" s="16"/>
       <c r="P29" s="16"/>
-      <c r="Q29" s="11"/>
-      <c r="R29" s="11"/>
-      <c r="S29" s="11"/>
-      <c r="T29" s="11"/>
+      <c r="Q29" s="16"/>
+      <c r="R29" s="16"/>
+      <c r="S29" s="16"/>
+      <c r="T29" s="16"/>
       <c r="U29" s="11"/>
       <c r="V29" s="11"/>
       <c r="W29" s="11"/>
@@ -4992,13 +5472,15 @@
         <v>108</v>
       </c>
       <c r="O30" s="22" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="P30" s="11"/>
       <c r="Q30" s="11"/>
       <c r="R30" s="11"/>
       <c r="S30" s="11"/>
-      <c r="T30" s="11"/>
+      <c r="T30" s="15">
+        <v>46297.45416666667</v>
+      </c>
       <c r="U30" s="11"/>
       <c r="V30" s="11"/>
       <c r="W30" s="11"/>
@@ -5050,7 +5532,9 @@
       <c r="Q31" s="11"/>
       <c r="R31" s="11"/>
       <c r="S31" s="11"/>
-      <c r="T31" s="11"/>
+      <c r="T31" s="15">
+        <v>46297.456250000003</v>
+      </c>
       <c r="U31" s="11"/>
       <c r="V31" s="11"/>
       <c r="W31" s="11"/>
@@ -5059,50 +5543,50 @@
       <c r="Z31" s="11"/>
     </row>
     <row r="32" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="11" t="s">
+      <c r="A32" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="B32" s="11" t="s">
+      <c r="B32" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="C32" s="12" t="s">
+      <c r="C32" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="D32" s="13" t="s">
+      <c r="D32" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="E32" s="11" t="s">
+      <c r="E32" s="16" t="s">
         <v>176</v>
       </c>
-      <c r="F32" s="11" t="s">
+      <c r="F32" s="16" t="s">
         <v>177</v>
       </c>
-      <c r="G32" s="11" t="s">
+      <c r="G32" s="16" t="s">
         <v>178</v>
       </c>
-      <c r="H32" s="14">
+      <c r="H32" s="17">
         <v>21999042857</v>
       </c>
-      <c r="I32" s="12" t="s">
+      <c r="I32" s="17" t="s">
         <v>179</v>
       </c>
-      <c r="J32" s="11"/>
-      <c r="K32" s="11"/>
-      <c r="L32" s="15">
+      <c r="J32" s="16"/>
+      <c r="K32" s="16"/>
+      <c r="L32" s="19">
         <v>46295.438888888886</v>
       </c>
-      <c r="M32" s="11"/>
-      <c r="N32" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="O32" s="13">
+      <c r="M32" s="18"/>
+      <c r="N32" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="O32" s="16">
         <v>46295.65902777778</v>
       </c>
-      <c r="P32" s="11"/>
-      <c r="Q32" s="11"/>
-      <c r="R32" s="11"/>
-      <c r="S32" s="11"/>
-      <c r="T32" s="11"/>
+      <c r="P32" s="16"/>
+      <c r="Q32" s="16"/>
+      <c r="R32" s="16"/>
+      <c r="S32" s="16"/>
+      <c r="T32" s="16"/>
       <c r="U32" s="11"/>
       <c r="V32" s="11"/>
       <c r="W32" s="11"/>
@@ -5154,7 +5638,9 @@
       <c r="Q33" s="11"/>
       <c r="R33" s="11"/>
       <c r="S33" s="11"/>
-      <c r="T33" s="11"/>
+      <c r="T33" s="15">
+        <v>46297.457638888889</v>
+      </c>
       <c r="U33" s="11"/>
       <c r="V33" s="11"/>
       <c r="W33" s="11"/>
@@ -5202,13 +5688,13 @@
         <v>39</v>
       </c>
       <c r="O34" s="18" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P34" s="16"/>
-      <c r="Q34" s="11"/>
-      <c r="R34" s="11"/>
-      <c r="S34" s="11"/>
-      <c r="T34" s="11"/>
+      <c r="Q34" s="16"/>
+      <c r="R34" s="16"/>
+      <c r="S34" s="16"/>
+      <c r="T34" s="16"/>
       <c r="U34" s="11"/>
       <c r="V34" s="11"/>
       <c r="W34" s="11"/>
@@ -5256,13 +5742,13 @@
         <v>39</v>
       </c>
       <c r="O35" s="18" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="P35" s="16"/>
-      <c r="Q35" s="11"/>
-      <c r="R35" s="11"/>
-      <c r="S35" s="11"/>
-      <c r="T35" s="11"/>
+      <c r="Q35" s="16"/>
+      <c r="R35" s="16"/>
+      <c r="S35" s="16"/>
+      <c r="T35" s="16"/>
       <c r="U35" s="11"/>
       <c r="V35" s="11"/>
       <c r="W35" s="11"/>
@@ -5310,13 +5796,13 @@
         <v>39</v>
       </c>
       <c r="O36" s="18" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="P36" s="16"/>
-      <c r="Q36" s="11"/>
-      <c r="R36" s="11"/>
-      <c r="S36" s="11"/>
-      <c r="T36" s="11"/>
+      <c r="Q36" s="16"/>
+      <c r="R36" s="16"/>
+      <c r="S36" s="16"/>
+      <c r="T36" s="16"/>
       <c r="U36" s="11"/>
       <c r="V36" s="11"/>
       <c r="W36" s="11"/>
@@ -5364,13 +5850,13 @@
         <v>39</v>
       </c>
       <c r="O37" s="18" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P37" s="16"/>
-      <c r="Q37" s="11"/>
-      <c r="R37" s="11"/>
-      <c r="S37" s="11"/>
-      <c r="T37" s="11"/>
+      <c r="Q37" s="16"/>
+      <c r="R37" s="16"/>
+      <c r="S37" s="16"/>
+      <c r="T37" s="16"/>
       <c r="U37" s="11"/>
       <c r="V37" s="11"/>
       <c r="W37" s="11"/>
@@ -5419,13 +5905,15 @@
         <v>46295.666666666664</v>
       </c>
       <c r="P38" s="11"/>
-      <c r="Q38" s="11"/>
-      <c r="R38" s="11"/>
-      <c r="S38" s="11"/>
-      <c r="T38" s="11"/>
-      <c r="U38" s="11"/>
-      <c r="V38" s="11"/>
-      <c r="W38" s="11"/>
+      <c r="Q38" s="43"/>
+      <c r="R38" s="43"/>
+      <c r="S38" s="43"/>
+      <c r="T38" s="44">
+        <v>46297.463194444441</v>
+      </c>
+      <c r="U38" s="45"/>
+      <c r="V38" s="45"/>
+      <c r="W38" s="45"/>
       <c r="X38" s="11"/>
       <c r="Y38" s="11"/>
       <c r="Z38" s="11"/>
@@ -5474,7 +5962,9 @@
       <c r="Q39" s="11"/>
       <c r="R39" s="11"/>
       <c r="S39" s="11"/>
-      <c r="T39" s="11"/>
+      <c r="T39" s="15">
+        <v>46297.464583333334</v>
+      </c>
       <c r="U39" s="11"/>
       <c r="V39" s="11"/>
       <c r="W39" s="11"/>
@@ -5526,7 +6016,9 @@
       <c r="Q40" s="11"/>
       <c r="R40" s="11"/>
       <c r="S40" s="11"/>
-      <c r="T40" s="11"/>
+      <c r="T40" s="15">
+        <v>46297.46597222222</v>
+      </c>
       <c r="U40" s="11"/>
       <c r="V40" s="11"/>
       <c r="W40" s="11"/>
@@ -5535,50 +6027,52 @@
       <c r="Z40" s="11"/>
     </row>
     <row r="41" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="11" t="s">
+      <c r="A41" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="B41" s="11" t="s">
+      <c r="B41" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="C41" s="12" t="s">
+      <c r="C41" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="D41" s="13" t="s">
+      <c r="D41" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="E41" s="16" t="s">
+        <v>210</v>
+      </c>
+      <c r="F41" s="16" t="s">
+        <v>211</v>
+      </c>
+      <c r="G41" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="H41" s="23">
+        <v>21981712143</v>
+      </c>
+      <c r="I41" s="17" t="s">
+        <v>213</v>
+      </c>
+      <c r="J41" s="16"/>
+      <c r="K41" s="16"/>
+      <c r="L41" s="34">
+        <v>46295.463888888888</v>
+      </c>
+      <c r="M41" s="16"/>
+      <c r="N41" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="E41" s="11" t="s">
-        <v>210</v>
-      </c>
-      <c r="F41" s="11" t="s">
-        <v>211</v>
-      </c>
-      <c r="G41" s="11" t="s">
-        <v>212</v>
-      </c>
-      <c r="H41" s="14">
-        <v>21981712143</v>
-      </c>
-      <c r="I41" s="12" t="s">
-        <v>213</v>
-      </c>
-      <c r="J41" s="11"/>
-      <c r="K41" s="11"/>
-      <c r="L41" s="33">
-        <v>46295.463888888888</v>
-      </c>
-      <c r="M41" s="11"/>
-      <c r="N41" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="O41" s="13" t="s">
-        <v>267</v>
-      </c>
-      <c r="P41" s="11"/>
-      <c r="Q41" s="11"/>
-      <c r="R41" s="11"/>
-      <c r="S41" s="11"/>
-      <c r="T41" s="11"/>
+      <c r="O41" s="37" t="s">
+        <v>266</v>
+      </c>
+      <c r="P41" s="16"/>
+      <c r="Q41" s="16"/>
+      <c r="R41" s="16"/>
+      <c r="S41" s="16"/>
+      <c r="T41" s="18" t="s">
+        <v>287</v>
+      </c>
       <c r="U41" s="11"/>
       <c r="V41" s="11"/>
       <c r="W41" s="11"/>
@@ -5620,19 +6114,19 @@
         <v>46295.465277777781</v>
       </c>
       <c r="M42" s="18" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="N42" s="18" t="s">
         <v>39</v>
       </c>
       <c r="O42" s="18" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="P42" s="16"/>
       <c r="Q42" s="16"/>
       <c r="R42" s="16"/>
-      <c r="S42" s="11"/>
-      <c r="T42" s="11"/>
+      <c r="S42" s="16"/>
+      <c r="T42" s="16"/>
       <c r="U42" s="11"/>
       <c r="V42" s="11"/>
       <c r="W42" s="11"/>
@@ -5641,50 +6135,52 @@
       <c r="Z42" s="11"/>
     </row>
     <row r="43" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="11" t="s">
+      <c r="A43" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="B43" s="11" t="s">
+      <c r="B43" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="C43" s="12" t="s">
+      <c r="C43" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="D43" s="13" t="s">
+      <c r="D43" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="E43" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="F43" s="16" t="s">
+        <v>217</v>
+      </c>
+      <c r="G43" s="16" t="s">
+        <v>218</v>
+      </c>
+      <c r="H43" s="23">
+        <v>22999995946</v>
+      </c>
+      <c r="I43" s="17" t="s">
+        <v>219</v>
+      </c>
+      <c r="J43" s="16"/>
+      <c r="K43" s="16"/>
+      <c r="L43" s="34">
+        <v>46295.467361111114</v>
+      </c>
+      <c r="M43" s="16"/>
+      <c r="N43" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="E43" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="F43" s="11" t="s">
-        <v>217</v>
-      </c>
-      <c r="G43" s="11" t="s">
-        <v>218</v>
-      </c>
-      <c r="H43" s="14">
-        <v>22999995946</v>
-      </c>
-      <c r="I43" s="12" t="s">
-        <v>219</v>
-      </c>
-      <c r="J43" s="11"/>
-      <c r="K43" s="11"/>
-      <c r="L43" s="33">
-        <v>46295.467361111114</v>
-      </c>
-      <c r="M43" s="11"/>
-      <c r="N43" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="O43" s="15">
+      <c r="O43" s="19">
         <v>46295.675694444442</v>
       </c>
-      <c r="P43" s="11"/>
-      <c r="Q43" s="11"/>
-      <c r="R43" s="11"/>
-      <c r="S43" s="11"/>
-      <c r="T43" s="11"/>
+      <c r="P43" s="16"/>
+      <c r="Q43" s="16"/>
+      <c r="R43" s="16"/>
+      <c r="S43" s="16"/>
+      <c r="T43" s="18" t="s">
+        <v>288</v>
+      </c>
       <c r="U43" s="11"/>
       <c r="V43" s="11"/>
       <c r="W43" s="11"/>
@@ -5726,19 +6222,19 @@
         <v>46295.479166666664</v>
       </c>
       <c r="M44" s="18" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="N44" s="18" t="s">
         <v>39</v>
       </c>
       <c r="O44" s="18" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P44" s="16"/>
       <c r="Q44" s="16"/>
       <c r="R44" s="16"/>
-      <c r="S44" s="11"/>
-      <c r="T44" s="11"/>
+      <c r="S44" s="16"/>
+      <c r="T44" s="16"/>
       <c r="U44" s="11"/>
       <c r="V44" s="11"/>
       <c r="W44" s="11"/>
@@ -5781,7 +6277,7 @@
       </c>
       <c r="M45" s="11"/>
       <c r="N45" s="13" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="O45" s="15">
         <v>46295.678472222222</v>
@@ -5790,7 +6286,9 @@
       <c r="Q45" s="11"/>
       <c r="R45" s="11"/>
       <c r="S45" s="11"/>
-      <c r="T45" s="11"/>
+      <c r="T45" s="15">
+        <v>46297.476388888892</v>
+      </c>
       <c r="U45" s="11"/>
       <c r="V45" s="11"/>
       <c r="W45" s="11"/>
@@ -5833,7 +6331,7 @@
       </c>
       <c r="M46" s="11"/>
       <c r="N46" s="13" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="O46" s="15">
         <v>46295.679861111108</v>
@@ -5842,7 +6340,9 @@
       <c r="Q46" s="11"/>
       <c r="R46" s="11"/>
       <c r="S46" s="11"/>
-      <c r="T46" s="11"/>
+      <c r="T46" s="15">
+        <v>46297.477777777778</v>
+      </c>
       <c r="U46" s="11"/>
       <c r="V46" s="11"/>
       <c r="W46" s="11"/>
@@ -5851,33 +6351,54 @@
       <c r="Z46" s="11"/>
     </row>
     <row r="47" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
+      <c r="A47" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="C47" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="D47" s="2"/>
-      <c r="E47" t="s">
+      <c r="D47" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="E47" s="18" t="s">
+        <v>278</v>
+      </c>
+      <c r="F47" s="18" t="s">
         <v>279</v>
       </c>
-      <c r="F47" t="s">
+      <c r="G47" s="18" t="s">
         <v>280</v>
       </c>
-      <c r="G47" t="s">
+      <c r="H47" s="18" t="s">
         <v>281</v>
       </c>
-      <c r="H47" t="s">
+      <c r="I47" s="17" t="s">
         <v>282</v>
       </c>
-      <c r="I47" t="s">
-        <v>283</v>
-      </c>
-      <c r="L47" s="39"/>
-      <c r="O47" s="39"/>
+      <c r="J47" s="16"/>
+      <c r="K47" s="16"/>
+      <c r="L47" s="19">
+        <v>46297.382638888892</v>
+      </c>
+      <c r="M47" s="18" t="s">
+        <v>244</v>
+      </c>
+      <c r="N47" s="18"/>
+      <c r="O47" s="19"/>
+      <c r="P47" s="16"/>
+      <c r="Q47" s="16"/>
+      <c r="R47" s="16"/>
+      <c r="S47" s="16"/>
+      <c r="T47" s="16"/>
+      <c r="U47" s="11"/>
+      <c r="V47" s="11"/>
+      <c r="W47" s="11"/>
+      <c r="X47" s="11"/>
+      <c r="Y47" s="11"/>
+      <c r="Z47" s="11"/>
     </row>
     <row r="48" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C48" s="1"/>
@@ -8743,24 +9264,24 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D47:D50" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D48:D50" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Ligar,Não atende/Ocupado,Retornar,Fora de Área/Caixa de Mensagens,Engano/Telefone Errado,Confirmado,Não Interessado,Recado"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="M2:N2 M4:N13 N17:N28 N30:N33 N36 N38:N43 D2:D46" xr:uid="{E6BDCAC1-495E-4F08-A2D4-CDCD12CD562F}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="M2:N2 M4:N13 N17:N28 N30:N33 N36 N38:N43 D2:D47" xr:uid="{B9E42BBD-482E-4D69-BF07-C1946310C66C}">
       <formula1>"Ligar,Não atende/Ocupado,Retornar,Fora de Área/Caixa de Mensagens,Engano/Telefone Errado,Confirmado,Não Interessado,Recado,Troca de Representante"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="I5" r:id="rId1" xr:uid="{62244F82-C0D6-428E-ABEB-7B909BE23778}"/>
-    <hyperlink ref="I6" r:id="rId2" xr:uid="{C0D9CB9D-CCB4-4503-8440-585809FE300C}"/>
-    <hyperlink ref="I40" r:id="rId3" xr:uid="{27A4EBF1-C632-46F9-A134-49FA33DBC229}"/>
+    <hyperlink ref="I5" r:id="rId1" xr:uid="{7B9598C3-A9C1-4CC2-8832-3434F87482C6}"/>
+    <hyperlink ref="I6" r:id="rId2" xr:uid="{D5F6A2C7-DF8A-4F53-AD8C-E4C99E514EC3}"/>
+    <hyperlink ref="I40" r:id="rId3" xr:uid="{CAD25BCA-2345-4A78-BA24-7733F0BB335A}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Z1000"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -8961,12 +9482,14 @@
       </c>
       <c r="N3" s="11"/>
       <c r="O3" s="13" t="s">
+        <v>272</v>
+      </c>
+      <c r="P3" s="13" t="s">
         <v>273</v>
       </c>
-      <c r="P3" s="13" t="s">
-        <v>274</v>
-      </c>
-      <c r="Q3" s="11"/>
+      <c r="Q3" s="13" t="s">
+        <v>289</v>
+      </c>
       <c r="R3" s="11"/>
       <c r="S3" s="11"/>
       <c r="T3" s="11"/>
@@ -9067,12 +9590,14 @@
       </c>
       <c r="N5" s="11"/>
       <c r="O5" s="13" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="P5" s="13" t="s">
-        <v>274</v>
-      </c>
-      <c r="Q5" s="11"/>
+        <v>273</v>
+      </c>
+      <c r="Q5" s="13" t="s">
+        <v>290</v>
+      </c>
       <c r="R5" s="11"/>
       <c r="S5" s="11"/>
       <c r="T5" s="11"/>
@@ -9221,7 +9746,7 @@
       <c r="M8" s="16"/>
       <c r="N8" s="16"/>
       <c r="O8" s="18" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="P8" s="16"/>
       <c r="Q8" s="16"/>
@@ -13210,9 +13735,9 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="I6" r:id="rId1" xr:uid="{CDAE194D-27B6-40C8-9A35-D6ED13AF423A}"/>
-    <hyperlink ref="I7" r:id="rId2" xr:uid="{EE161692-2FAA-474A-BECF-9908F71386D4}"/>
-    <hyperlink ref="I8" r:id="rId3" xr:uid="{C777FC11-83FF-402F-BEC1-A5A96902E9DC}"/>
+    <hyperlink ref="I6" r:id="rId1" xr:uid="{13FDB5C5-1556-47DD-B017-C4AA6F1B7F09}"/>
+    <hyperlink ref="I7" r:id="rId2" xr:uid="{EDE17627-4B5D-4282-B53C-5A739DD054C9}"/>
+    <hyperlink ref="I8" r:id="rId3" xr:uid="{543F5972-1643-4671-9FF0-CE05DE956F61}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
